--- a/multi_period_routing/results/summary_results_new.xlsx
+++ b/multi_period_routing/results/summary_results_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eashw\Desktop\PhD_resesarch\multi-period-MD-RPP-RRV\multi_period_routing\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996A5460-4067-48B8-951C-DA0220702718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D00FF9-11E7-4421-B139-F45D49721EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35978" yWindow="3697" windowWidth="17280" windowHeight="9983" xr2:uid="{993A7F5B-E494-4100-B59B-AD5C5E3EBF65}"/>
+    <workbookView xWindow="1830" yWindow="1830" windowWidth="17280" windowHeight="9984" xr2:uid="{993A7F5B-E494-4100-B59B-AD5C5E3EBF65}"/>
   </bookViews>
   <sheets>
     <sheet name="summary_results_new" sheetId="1" r:id="rId1"/>
@@ -52,16 +52,16 @@
     <t>Interval</t>
   </si>
   <si>
-    <t>SA+PMFR</t>
+    <t>Approach</t>
   </si>
   <si>
-    <t>SA+PMFR + Exact Cache</t>
+    <t>SA</t>
   </si>
   <si>
-    <t>SA+PMFR + Exact Cache + LTMB</t>
+    <t>SA + Exact Cache</t>
   </si>
   <si>
-    <t>Approach</t>
+    <t>SA + LTMB</t>
   </si>
 </sst>
 </file>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
@@ -974,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -1079,7 +1079,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
@@ -1289,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1324,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -1359,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -1394,7 +1394,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
@@ -1464,7 +1464,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -1499,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
@@ -1534,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
@@ -1639,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -1674,7 +1674,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -1744,7 +1744,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
@@ -1779,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
@@ -1814,7 +1814,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -1919,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="1">
         <v>3</v>
@@ -1954,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -2024,7 +2024,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1">
         <v>2</v>
@@ -2059,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33" s="1">
         <v>3</v>
@@ -2094,7 +2094,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
@@ -2164,7 +2164,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
@@ -2199,7 +2199,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
@@ -2234,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
@@ -2304,7 +2304,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
@@ -2339,7 +2339,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1">
         <v>3</v>
@@ -2374,7 +2374,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" s="1">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
@@ -2444,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1">
         <v>2</v>
@@ -2479,7 +2479,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1">
         <v>3</v>
@@ -2514,7 +2514,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" s="1">
         <v>0</v>
@@ -2549,7 +2549,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
@@ -2584,7 +2584,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
@@ -2654,7 +2654,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C52" s="1">
         <v>2</v>
@@ -2759,7 +2759,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="1">
         <v>3</v>
@@ -2794,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55" s="1">
         <v>1</v>
@@ -2864,7 +2864,7 @@
         <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
@@ -2899,7 +2899,7 @@
         <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C57" s="1">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>5</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
@@ -3004,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1">
         <v>2</v>
@@ -3039,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1">
         <v>3</v>
@@ -3074,7 +3074,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
@@ -3144,7 +3144,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -3179,7 +3179,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="1">
         <v>3</v>
@@ -3214,7 +3214,7 @@
         <v>6</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1">
         <v>1</v>
@@ -3284,7 +3284,7 @@
         <v>6</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1">
         <v>2</v>
@@ -3319,7 +3319,7 @@
         <v>6</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1">
         <v>3</v>
@@ -3354,7 +3354,7 @@
         <v>6</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
@@ -3424,7 +3424,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C72" s="1">
         <v>2</v>
@@ -3459,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="1">
         <v>3</v>
@@ -3494,7 +3494,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74" s="1">
         <v>0</v>
@@ -3529,7 +3529,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" s="1">
         <v>2</v>
@@ -3599,7 +3599,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" s="1">
         <v>3</v>
@@ -3634,7 +3634,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C78" s="1">
         <v>0</v>
@@ -3669,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C79" s="1">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C80" s="1">
         <v>2</v>
@@ -3739,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C81" s="1">
         <v>3</v>
@@ -3774,7 +3774,7 @@
         <v>7</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C82" s="1">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>7</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
@@ -3844,7 +3844,7 @@
         <v>7</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
@@ -3879,7 +3879,7 @@
         <v>7</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="1">
         <v>3</v>
@@ -3914,7 +3914,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
@@ -3984,7 +3984,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" s="1">
         <v>2</v>
@@ -4019,7 +4019,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" s="1">
         <v>3</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
@@ -4089,7 +4089,7 @@
         <v>8</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C91" s="1">
         <v>1</v>
@@ -4124,7 +4124,7 @@
         <v>8</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
@@ -4159,7 +4159,7 @@
         <v>8</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" s="1">
         <v>3</v>
@@ -4194,7 +4194,7 @@
         <v>8</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C94" s="1">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>8</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="1">
         <v>1</v>
@@ -4264,7 +4264,7 @@
         <v>8</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C96" s="1">
         <v>2</v>
@@ -4299,7 +4299,7 @@
         <v>8</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C97" s="1">
         <v>3</v>
@@ -4334,7 +4334,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
@@ -4369,7 +4369,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C99" s="1">
         <v>1</v>
@@ -4404,7 +4404,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" s="1">
         <v>2</v>
@@ -4439,7 +4439,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C101" s="1">
         <v>3</v>
@@ -4474,7 +4474,7 @@
         <v>9</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>9</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" s="1">
         <v>1</v>
@@ -4544,7 +4544,7 @@
         <v>9</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1">
         <v>2</v>
@@ -4579,7 +4579,7 @@
         <v>9</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C105" s="1">
         <v>3</v>
@@ -4614,7 +4614,7 @@
         <v>9</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>9</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C107" s="1">
         <v>1</v>
@@ -4684,7 +4684,7 @@
         <v>9</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C108" s="1">
         <v>2</v>
@@ -4719,7 +4719,7 @@
         <v>9</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C109" s="1">
         <v>3</v>
@@ -4754,7 +4754,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -4789,7 +4789,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C111" s="1">
         <v>1</v>
@@ -4824,7 +4824,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
@@ -4859,7 +4859,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" s="1">
         <v>3</v>
@@ -4894,7 +4894,7 @@
         <v>10</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -4964,7 +4964,7 @@
         <v>10</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C116" s="1">
         <v>2</v>
@@ -4999,7 +4999,7 @@
         <v>10</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C117" s="1">
         <v>3</v>
@@ -5034,7 +5034,7 @@
         <v>10</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -5069,7 +5069,7 @@
         <v>10</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C119" s="1">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         <v>10</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -5139,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C121" s="1">
         <v>3</v>
@@ -5174,7 +5174,7 @@
         <v>11</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
@@ -5209,7 +5209,7 @@
         <v>11</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C123" s="1">
         <v>1</v>
@@ -5244,7 +5244,7 @@
         <v>11</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -5279,7 +5279,7 @@
         <v>11</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C125" s="1">
         <v>3</v>
@@ -5314,7 +5314,7 @@
         <v>11</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>11</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C127" s="1">
         <v>1</v>
@@ -5384,7 +5384,7 @@
         <v>11</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C128" s="1">
         <v>2</v>
@@ -5419,7 +5419,7 @@
         <v>11</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C129" s="1">
         <v>3</v>
@@ -5454,7 +5454,7 @@
         <v>11</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C130" s="1">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>11</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C131" s="1">
         <v>1</v>
@@ -5524,7 +5524,7 @@
         <v>11</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -5559,7 +5559,7 @@
         <v>11</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C133" s="1">
         <v>3</v>
@@ -5594,7 +5594,7 @@
         <v>12</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>12</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C135" s="1">
         <v>1</v>
@@ -5664,7 +5664,7 @@
         <v>12</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -5699,7 +5699,7 @@
         <v>12</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C137" s="1">
         <v>3</v>
@@ -5734,7 +5734,7 @@
         <v>12</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C139" s="1">
         <v>1</v>
@@ -5804,7 +5804,7 @@
         <v>12</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -5839,7 +5839,7 @@
         <v>12</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C141" s="1">
         <v>3</v>
@@ -5874,7 +5874,7 @@
         <v>12</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C142" s="1">
         <v>0</v>
@@ -5909,7 +5909,7 @@
         <v>12</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C143" s="1">
         <v>1</v>
@@ -5944,7 +5944,7 @@
         <v>12</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -5979,7 +5979,7 @@
         <v>12</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C145" s="1">
         <v>3</v>
@@ -6014,7 +6014,7 @@
         <v>13</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146" s="1">
         <v>0</v>
@@ -6049,7 +6049,7 @@
         <v>13</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C147" s="1">
         <v>1</v>
@@ -6084,7 +6084,7 @@
         <v>13</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C148" s="1">
         <v>2</v>
@@ -6119,7 +6119,7 @@
         <v>13</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C149" s="1">
         <v>3</v>
@@ -6154,7 +6154,7 @@
         <v>13</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C150" s="1">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>13</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C151" s="1">
         <v>1</v>
@@ -6224,7 +6224,7 @@
         <v>13</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C152" s="1">
         <v>2</v>
@@ -6259,7 +6259,7 @@
         <v>13</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C153" s="1">
         <v>3</v>
@@ -6294,7 +6294,7 @@
         <v>13</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C154" s="1">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>13</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C155" s="1">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>13</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C156" s="1">
         <v>2</v>
@@ -6399,7 +6399,7 @@
         <v>13</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C157" s="1">
         <v>3</v>
@@ -6434,7 +6434,7 @@
         <v>14</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C158" s="1">
         <v>0</v>
@@ -6469,7 +6469,7 @@
         <v>14</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C159" s="1">
         <v>1</v>
@@ -6504,7 +6504,7 @@
         <v>14</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" s="1">
         <v>2</v>
@@ -6539,7 +6539,7 @@
         <v>14</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C161" s="1">
         <v>3</v>
@@ -6574,7 +6574,7 @@
         <v>14</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C162" s="1">
         <v>0</v>
@@ -6609,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C163" s="1">
         <v>1</v>
@@ -6644,7 +6644,7 @@
         <v>14</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C164" s="1">
         <v>2</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C165" s="1">
         <v>3</v>
@@ -6714,7 +6714,7 @@
         <v>14</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C166" s="1">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>14</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C167" s="1">
         <v>1</v>
@@ -6784,7 +6784,7 @@
         <v>14</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C168" s="1">
         <v>2</v>
@@ -6819,7 +6819,7 @@
         <v>14</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C169" s="1">
         <v>3</v>
@@ -6854,7 +6854,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C170" s="1">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C171" s="1">
         <v>1</v>
@@ -6924,7 +6924,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C172" s="1">
         <v>2</v>
@@ -6959,7 +6959,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" s="1">
         <v>3</v>
@@ -6994,7 +6994,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C174" s="1">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C175" s="1">
         <v>1</v>
@@ -7064,7 +7064,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C176" s="1">
         <v>2</v>
@@ -7099,7 +7099,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C177" s="1">
         <v>3</v>
@@ -7134,7 +7134,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C178" s="1">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C179" s="1">
         <v>1</v>
@@ -7204,7 +7204,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C180" s="1">
         <v>2</v>
@@ -7239,7 +7239,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C181" s="1">
         <v>3</v>
